--- a/Pravartiya/data/output_excels/newsletter_2026-04-01_to_2026-04-30/SEBI_Newsletter.xlsx
+++ b/Pravartiya/data/output_excels/newsletter_2026-04-01_to_2026-04-30/SEBI_Newsletter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,133 +499,295 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Securities and Exchange Board of India (Real Estate Investment Trusts) (Amendment) Regulations, 2026</t>
+          <t>Securities and Exchange Board of India (Intermediaries) (Amendment) Regulations, 2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776658226643.pdf</t>
+          <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776419077625.pdf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Securities_and_Exchange_Board_of_India_Real_Estate_Investment_Trusts_Amendment_R_69349c5e.pdf</t>
+          <t>Securities_and_Exchange_Board_of_India_Intermediaries_Amendment_Regulations_2026_1c146097.pdf</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/April/Securities_and_Exchange_Board_of_India_Real_Estate_Investment_Trusts_Amendment_R_69349c5e.pdf</t>
+          <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/April/Securities_and_Exchange_Board_of_India_Intermediaries_Amendment_Regulations_2026_1c146097.pdf</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16th April, 2026</t>
+          <t>15th April, 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Securities and Exchange Board of India (Real Estate Investment Trusts) (Amendment) Regulations, 2026 dated 2026-04-18
-Effective date - 16th April, 2026</t>
+          <t>Securities and Exchange Board of India (Intermediaries) (Amendment) Regulations, 2026 dated 2026-04-16
+Effective date - 15th April, 2026
+**SEBI Newsletter**
+**Date:** 2026-04-16
+**Effective Date:** 15th April, 2026
+**Amendments to Intermediaries Regulations**
+- SEBI has amended the Intermediaries Regulations with an effective date of 15th April, 2026. The key changes include:
+  1. **New Definition:** "days" is now defined as calendar days unless otherwise specified in these regulations (Clause 1e).
+  2. **Modification to Existing Definitions:** The term "self regulatory organization" now includes a stock exchange (Clause j modified and n inserted).
+  3. **Change in Application Process:** An application for grant of a certificate will be processed from the commencement of these regulations onwards (Chapter II, Clause 3).
+**Existing Provision Prior to Amendment**
+- The term "days" was not specifically defined and its interpretation varied contextually. The definition of "self regulatory organization" did not include a stock exchange. Applications for grant of a certificate were processed from the date specified in each regulation.
+**Compliance Implication**
+- Intermediaries are advised to review their processes related to days calculation, self regulatory organization recognition, and application procedures for grant of certificates in light of these amendments.
+**Action Point for Listed Entities/Intermediaries:**
+- Review and update internal policies and procedures as necessary to comply with the new definitions and application process.
+**SEBI Newsletter Summary - Amendments to Fit and Proper Criteria**
+Date: 16th April, 2026
+Effective Date: 15th April, 2026
+**Amendment Overview:**
+- SEBI has amended the fit and proper criteria for applicants, intermediaries, and key persons in the Securities and Exchange Board of India (Intermediaries) Regulations.
+**Key Changes:**
+1. **Substitution:** The clause "not incurring any of the following disqualifications" has been replaced with a more detailed list of events that may disqualify a person.
+2. **Omission:** Certain provisions, such as criminal complaint or information pending and charge sheet by enforcement agencies, have been removed.
+3. **Insertion:** New criteria include conviction for economic offences or offences involving moral turpitude, order for winding up, and declaration as a fugitive economic offender.
+**Existing Provision Prior to Amendment:**
+The provisions were broadly focused on integrity, honesty, ethical behavior, reputation, fairness, character, and certain disqualifying events for key persons.
+**Compliance Implication:**
+Listed entities and intermediaries must review their key personnel's status against the updated criteria to ensure compliance. They should also monitor for any subsequent changes in the fit and proper criteria as specified by SEBI from time to time.
+**Action Point for Listed Entities/Intermediaries:**
+- Review the fit and proper criteria of all key personnel according to the updated list provided.
+- Implement a monitoring system to keep track of any changes in the fit and proper criteria and ensure ongoing compliance.
+**SEBI Newsletter Summary**
+**Date of Circular:** 16th April, 2026
+**Effective Date:** 15th April, 2026
+**Amendment Announcement**
+SEBI has amended the 'fit and proper person' criteria for applicants, intermediaries, and key individuals associated with them. The changes focus on enhancing the screening process to ensure higher standards of integrity and accountability.
+**Gist of Amendment**
+- Substituted the existing criteria disqualifying persons from being 'fit and proper' with a new list of events that would make them ineligible, including recovery proceedings, orders for winding up, or any offence involving moral turpitude.
+- Omitted the requirement of a criminal complaint or information pending against an individual to be considered as disqualifying.
+- Introduced a 15-day reporting timeframe for applicants or intermediaries when any person under the amended criteria is subjected to events listed.
+**Existing Provision Prior to Amendment**
+The previous provision included disqualifications such as pending criminal complaints, charges against individuals, and winding up proceedings.
+**Compliance Implications**
+- Intermediaries should review their key personnel and ensure they meet the new 'fit and proper person' criteria.
+- Monitor ongoing recovery proceedings or court cases concerning applicants or intermediaries to comply with the 15-day reporting requirement.
+**SEBI Newsletter Summary**
+**Date:** 16th April, 2026
+**Effective Date:** 15th April, 2026
+**SEBI has revised the 'fit and proper person' criteria for applicants and intermediaries**
+- The amended provision now includes persons holding twenty percent or more voting rights in an unlisted applicant or intermediary, irrespective of whether they hold controlling interest or exercise control.
+- Previously, only the principal officer, directors, managing partners, compliance officer, key management persons, promoters, persons holding controlling interest, and those exercising control were required to meet the 'fit and proper person' criteria.
+**Existing provision prior to amendment**
+- The applicant or intermediary; the principal officer, the directors or managing partners, the compliance officer and the key management persons by whatever name called; and the promoters or persons holding controlling interest or persons exercising control over the applicant or intermediary, directly or indirectly were required to meet the 'fit and proper person' criteria.
+- In case of an unlisted applicant or intermediary, only those persons holding more than 20% voting rights who also held controlling interest or exercised control were subjected to this criterion.
+**What changed:**
+- The requirement for a person to not incur any disqualifications has been substituted with the specific events that would lead to a person being deemed unfit. These include but are not limited to: orders of restraint, prohibition or debarment by regulatory authorities, conviction for economic offenses, securities laws offenses or offenses involving moral turpitude, winding up, insolvency, and categorization as a wilful defaulter among others.
+- Certain provisions have been omitted, such as the filing of criminal complaints or information under section 154 of the Code of Criminal Procedure, charge sheets filed by enforcement agencies in matters concerning economic offenses, and winding up proceedings initiated against a person.
+**Compliance Implication:**
+- Applicants and intermediaries are required to inform SEBI within fifteen working days if any person under clause (2) is subjected to any event under sub-clause (b) of clause (3).
+- Individuals declared as not 'fit and proper persons' by an order of the Board will be ineligible for registration during the period provided in the said order.
+SEBI has amended the Intermediaries Regulations with effect from 15th April, 2026.
+- The provision regarding disqualification of an associate or group entity now states that such a declaration shall not have any bearing on the 'fit and proper person' criteria of the applicant or intermediary unless they are also found to be subjected to the same event. Previously, the provision stated that the disqualification would only impact the 'fit and proper person' criteria if the applicant or intermediary incurred the same disqualification in the same matter.
+- The amendment includes a new provision stating that if any person as referred in sub-clause (b) of clause (2) has been declared as not ‘fit and proper person’ by the Board, the intermediary shall replace such person within thirty working days from the date of declaration, failing which the 'fit and proper person' criteria may be invoked against the intermediary. Previously, there was no such specific provision regarding replacement of persons in this scenario.
+- Compliance implication: Intermediaries are now required to closely monitor their associate or group entities for any disqualifications that might impact their own 'fit and proper person' status. In case a person referred in sub-clause (b) of clause (2) is declared not ‘fit and proper’, the intermediary must replace such person within the stipulated time period to avoid potential regulatory action.
+Action point for listed entities/intermediaries: Ensure that all associates and group entities are monitored for any disqualifications that could impact their 'fit and proper person' status. In case a person referred in sub-clause (b) of clause (2) is declared not ‘fit and proper’, replace such person within the stipulated time period to maintain regulatory compliance.
+**SEBI Newsletter Summary**
+**Date:** 16th April, 2026
+**Effective Date:** 15th April, 2026
+**Amendment Announcement:** SEBI has amended the 'Fit and Proper Person' criteria for applicants and intermediaries.
+**Gist of Amendment:** The provision "not incurring any disqualifications" has been substituted with a detailed list of events that may lead to a person being deemed unfit. These events include orders against the person by SEBI or other regulatory authorities, pending recovery proceedings, convictions for economic offences or securities laws violations, insolvency, wilful defaulter status, and more.
+**Existing Provision:** Previously, a person was considered fit and proper if they did not incur any disqualifications.
+**What Changed:** The list of potential disqualifying events has been expanded and detailed.
+**Compliance Implication:** Listed entities and intermediaries must ensure that all applicants, directors, managing partners, compliance officers, key management persons, promoters, controlling interest holders, and those holding 20% or more voting rights meet the updated 'Fit and Proper Person' criteria. They should also inform SEBI within 15 working days if any person under their purview is subjected to any of the events listed in the amended provision.
+**Action Point:** Review and update your records to ensure compliance with the new 'Fit and Proper Person' criteria. Monitor for any events that may lead to disqualification among relevant individuals in your organization, and inform SEBI promptly if such events occur.
+**SEBI Newsletter Summary**
+Subject: Amendments to SEBI (Intermediaries) Regulations, 2008 - Key Highlights
+Date: April 16, 2026
+Effective Date: April 15, 2026
+- SEBI has introduced a new provision defining the term "days" as calendar days, unless otherwise specified in these regulations.
+Existing Provision: The term "days" was not specifically defined within the regulations.
+What Changed: The amendment provides clarity on what constitutes a day for the purpose of these regulations.
+Compliance Implication: Entities and intermediaries must ensure they understand and adhere to the new definition of "days" when calculating timeframes or deadlines stipulated in their obligations under the regulations.
+Action Point: Review internal policies, procedures, and calculations related to timelines to incorporate the updated definition of "days."
+**SEBI Newsletter Summary**
+*SEBI has revised certain provisions related to 'Fit and Proper' criteria for intermediaries, effective from 15th April, 2026.*
+- Date of Circular: 16th April, 2026
+- Effective Date: 15th April, 2026
+**Changes Introduced:**
+1. The duration for which a person declared unfit by SEBI is barred from applying for registration has been modified. Previously, the person was barred for the period specified in the order or five years from the date of effect of the order, if no such period was specified. Now, the person will be barred for the period specified in the order.
+2. The time frame for considering an application for registration as an intermediary when a notice to show cause has been issued against the applicant or any other person referred in clause (2) has been amended. Earlier, the application was not considered for a period of one year from the date of issuance of such notice. Now, the application will not be considered for a period of six months from the date of issuance of such notice or until the conclusion of the proceedings, whichever is earlier.
+3. The provision regarding the disqualification of an associate or group entity of the applicant or intermediary has been substituted. Now, if an associate or group entity of the applicant or intermediary has been declared as not 'fit and proper person' by SEBI, such declaration shall not have any bearing on the 'fit and proper person' criteria of the applicant or intermediary unless the applicant or intermediary or any other person referred in clause (2) is also found to be subjected to the same event.
+**Existing Provision Prior to Amendment:**
+Please refer to the provided text for details on the existing provisions prior to amendment.
+**Compliance Implication:**
+The intermediaries are advised to ensure that their applications for registration comply with the revised provisions, particularly in relation to notices to show cause and disqualifications of associates or group entities. They should also be prepared to adhere to any orders issued by SEBI regarding fitness and propriety criteria.
+**Action Point:**
+Intermediaries are advised to review their compliance procedures in light of the amendments and ensure they are in line with the revised regulations.
+**SEBI Newsletter Summary - April 2026**
+Dear Listed Entities and Intermediaries,
+We are pleased to announce that SEBI has amended the Intermediaries Regulations on 15th April, 2026. The changes aim to enhance transparency and strengthen regulatory oversight. Here's a summary of the key modifications:
+- **Effective Date**: 15th April, 2026
+- **Gist of Amendment**: SEBI has introduced clarifications regarding the definition of 'principal officer'. This includes adding key employees and any person designated as a principal officer under relevant regulations.
+- **Existing Provision Prior to Amendment**: The provision previously specified proprietors, partners, whole time/executive directors/managing directors, trustees, and persons designated as principal officers under relevant regulations.
+- **What Changed**: The definition of 'principal officer' has been expanded to include key employees and any person designated as a principal officer under relevant regulations.
+- **Compliance Implication**: Listed entities and intermediaries should review their organizational structures to ensure all principal officers are appropriately identified and managed according to the updated regulations.
+Action Point: Review and update organizational structure and designation processes to accommodate the new definition of 'principal officer'.
+For more detailed information, please refer to the official circular issued by SEBI on the specified date.
+Best Regards,
+Pravartiya Team
+**SEBI Newsletter Summary**
+Date: April 16, 2026
+Effective Date: April 15, 2026
+**SEBI has amended the Intermediaries Regulations to clarify and expand certain definitions.**
+- Prior to this amendment, "change in control," "control," and "corporate restructuring" were defined in relation to intermediaries. The new amendments provide further clarity by including more detailed descriptions of each term.
+- Under the revised definition, "corporate restructuring" now encompasses amalgamation, demerger, consolidation or any other kind of reorganization that falls under Section 391 of the Companies Act 1956 or any equivalent provision in subsequent laws.
+- The new addition "change of status or constitution" further expands on corporate restructuring to include agreements or arrangements that would have similar effects.
+- The term "associate" has also been added, defining it as any person controlled directly or indirectly by the intermediary, any person who controls the intermediary in a similar manner, or any entity or person under common control with the intermediary.
+*Existing provision prior to amendment:*
+- "Change in control," "control," and "corporate restructuring" were defined in relation to intermediaries but without detailed descriptions.
+- The term "associate" was not explicitly mentioned.
+*Compliance Implication:*
+Listed entities/intermediaries are advised to familiarize themselves with the updated definitions and revised provisions. Any changes in status, constitution, or control should be communicated to SEBI promptly as per the relevant regulations.
+**SEBI Newsletter Summary**
+**Date:** April 15, 2026
+**Amendment Announcement:** SEBI has amended the Intermediaries Regulations. The changes are effective from April 15, 2026.
+**Key Highlights:**
+1. **Expanded Definition of Control:** The definition of "control" in relation to an intermediary now includes the power to, directly or indirectly, control the management or policy decisions by person(s) acting individually or in concert. This expansion aims to address potential conflicts of interest and ensure better oversight.
+2. **Clarification on Days:** The term "days" now means calendar days, unless otherwise specified in these regulations. This clarification provides a standard definition for the interpretation of timeframes.
+3. **Intermediary Definition:** The amendments provide a more detailed and comprehensive list of entities that fall under the umbrella term "intermediary," including FPIs, trading members of derivative segments, etc., while excluding specific categories such as foreign venture capital investors, mutual funds, collective investment schemes, and venture capital funds.
+4. **Changes in Legal Status:** The amendment includes a new provision for addressing changes in the legal status of intermediaries, ensuring that any alterations to their organizational structure are properly addressed by SEBI regulations.
+5. **Action Point:** Listed entities/intermediaries should review their organizational structures and control mechanisms to ensure compliance with the expanded definition of "control." They should also familiarize themselves with the new provisions related to changes in legal status and days' calculation to adapt accordingly.
+**SEBI Newsletter Summary**
+**Date:** 16th April, 2026
+**Effective Date:** 15th April, 2026
+**Amendments to SEBI (Intermediaries) Regulations, 2026**
+- SEBI has amended the Intermediaries Regulations, introducing new provisions and revising existing ones.
+**Key Changes**
+1. A new provision (3A) requires intermediaries or applicants to inform the Board within fifteen working days if any person under clause (2) is subjected to events listed in sub-clause (b) of clause (3).
+2. The period for which a person declared unfit and proper cannot apply for registration has been revised. The period specified in the order will no longer include a default provision of five years if none is provided in the order.
+3. The timeframe for considering applications for intermediary registration when a notice to show cause has been issued has been revised from one year to six months.
+4. The provision regarding the bearing of disqualifications of associate or group entities on the 'fit and proper person' criteria of the applicant or intermediary has been substituted, with clearer language and conditions specified.
+**Prior Existing Provisions**
+- Prior to amendment, there were no provisions equivalent to (3A) and (6) as they have been newly inserted.
+- The previous provision in clause (4) included a default period of five years if no specific period was provided in the order.
+- The previous provision in clause (6) was more complex and had additional conditions not present in the revised version.
+**Compliance Implications**
+- Intermediaries must promptly inform the Board of any events that could lead to disqualification of a person under clause (2).
+- Applicants and intermediaries should be aware of the revised timeframes for considering registration applications when a notice to show cause has been issued.
+- When associates or group entities are declared unfit and proper, intermediaries must adhere to the new conditions specified in the substituted provision (6).
+**Action Point for Listed Entities/Intermediaries:**
+- Review your current processes to ensure compliance with the revised regulations.
+- Keep updated on any further amendments or clarifications from SEBI.
+**SEBI Newsletter Summary**
+Dear Listed Entities and Intermediaries,
+We are pleased to inform you about the amendments introduced by SEBI in its regulations effective from 15th April, 2026.
+1. **Newly Inserted Provision**: The term "days" has been defined to mean calendar days unless otherwise specified in these regulations.
+Prior to this amendment, there was no specific definition for the term "days." This change will clarify the interpretation of timeframes in various regulations.
+2. **Change in Application Process**: An applicant seeking registration as a stock broker, sub-broker, trading member, clearing member, or depository participant must now make their application through the respective stock exchange, clearing corporation, or depository they are affiliated with.
+Previously, applicants made applications directly to the Board. This change aims to streamline the application process and improve coordination between intermediaries and regulatory bodies.
+3. **Compliance Implication**: Intermediaries planning to apply for registration should ensure they submit their applications through the correct channels as specified above to avoid delays or rejections.
+For further details, please refer to the SEBI (Intermediaries) (Amendment) Regulations, 2026.
+Action Point: Update your application procedures to comply with the new regulations when applying for registration as an intermediary.
+Best Regards,
+The SEBI Team
+**SEBI Newsletter Summary**
+Date: 16th April, 2026
+Effective Date: 15th April, 2026
+**SEBI Has Amended the Intermediaries Regulations**
+- The Securities and Exchange Board of India (Intermediaries) (Amendment) Regulations, 2026 introduces a new provision.
+- This amendment alters the criteria for declaring a person or entity as 'not fit and proper'.
+Gist of Amendment:
+- A person will be declared 'not fit and proper' by the Board if they are categorized as a wilful defaulter, declared a fugitive economic offender, or subjected to any event specified by the Board.
+- The period for which a person declared unfit cannot apply for registration has been omitted from the regulations.
+- The timeframe for an intermediary to replace an unfit person has been reduced to 30 working days, from the date of recognition by stock exchanges.
+- The provision regarding disqualification of associate or group entities has been substituted, and now applies if the applicant or intermediary is also subjected to the same event.
+Existing Provision Prior to Amendment:
+- A person declared unfit could not apply for registration during a specified period, as determined by the order.
+- The intermediary had to replace an unfit person within 30 days if they failed to satisfy the 'fit and proper' criteria.
+- Disqualification of associate or group entities had no bearing on the 'fit and proper' criteria unless the same disqualification was incurred by the applicant or intermediary.
+What Changed:
+- The period for which a person declared unfit cannot apply for registration is now omitted from the regulations.
+- The timeframe for an intermediary to replace an unfit person has been reduced.
+- The provision regarding disqualification of associate or group entities has been substituted, and now applies if the applicant or intermediary is also subjected to the same event.
+What Existed Earlier:
+- A person declared unfit could not apply for registration during a specified period as determined by the order.
+- The intermediary had to replace an unfit person within 30 days if they failed to satisfy the 'fit and proper' criteria.
+- Disqualification of associate or group entities only affected the 'fit and proper' criteria if the same disqualification was incurred by the applicant or intermediary.
+Compliance Implication:
+- Intermediaries must ensure they comply with the new reduced timeframe for replacing unfit persons.
+- Intermediaries should review their associated entities to ensure they are not subjected to any events that could affect their 'fit and proper' status.
+Action Point for Listed Entities/Intermediaries:
+Review your current status regarding events under sub-clause (b) of clause (3), as well as the status of your associate or group entities, to ensure compliance with the new regulations. Update your internal policies and procedures accordingly.
+**SEBI Newsletter Summary - Amendments to Fit and Proper Person Criteria**
+Issue Date: 16th April, 2026
+Effective Date: 15th April, 2026
+- SEBI has amended the criteria for determining a 'fit and proper person' in the Securities and Exchange Board of India (Intermediaries) Regulations.
+Gist of Amendment:
+- The new provision introduces the requirement for recovery proceedings against an individual to be pending or an order of conviction for any economic offence, securities laws offence, or offence involving moral turpitude to disqualify a person from being deemed 'fit and proper'. Prior to this amendment, such disqualification was based on criminal complaints or chargesheets.
+- The provision regarding winding up proceedings against an individual has also been clarified, with the omission of the phrase "any winding up proceedings have been initiated or".
+Existing Provision Prior to Amendment:
+Criminal complaints or information under section 154 of the Code of Criminal Procedure, 1973 (2 of 1974) against an individual by the Board and chargesheets filed against an individual in matters concerning economic offences were grounds for disqualification.
+What Changed:
+The amended provisions introduce new grounds for disqualification based on recovery proceedings against an individual for any economic offence, securities laws offence, or offence involving moral turpitude and provide clarity on winding up proceedings against an individual.
+Compliance Implication:
+Intermediaries are required to inform the Board of any occurrence of events under sub-clause (b) of clause (3) within fifteen working days of recognition by stock exchanges. Additionally, individuals declared not 'fit and proper' will be ineligible for registration during the specified period outlined in the order of the Board.
+Action Point:
+Listed entities and intermediaries are advised to review their internal compliance procedures in light of these amendments and ensure timely reporting of relevant events to the Board.
+**SEBI Newsletter Summary**
+Date: April 16, 2026
+Effective Date: April 15, 2026
+**SEBI has amended the 'fit and proper person' criteria for applicants and intermediaries**
+- The amendment expands the factors considered for determining a 'fit and proper person', including events such as orders of conviction for economic offenses, offenses involving moral turpitude, or being categorized as a wilful defaulter.
+- Prior to this amendment, the criteria focused on disqualifications like restraint, prohibition, or debarment orders, recovery proceedings, criminal complaints, charge sheets, winding up orders, insolvency, and other disqualifications as specified by SEBI.
+- Compliance Implication: Listed entities and intermediaries should review their key management persons, promoters, and persons holding controlling interest to ensure they meet the updated 'fit and proper person' criteria. This includes checking for any past convictions or categorizations that may disqualify them.
+Action Point for Listed Entities/Intermediaries: Conduct a comprehensive review of your key management team and persons with significant influence in accordance with the revised 'fit and proper person' criteria.
+SEBI has amended regulations related to intermediaries effective from 15th April, 2026.
+**Key Changes:**
+1. New clause 32(3A) introduces a requirement for applicants or intermediaries to inform the Board of any event under sub-clause (b) of clause (3) within fifteen working days of recognition by stock exchanges.
+2. Clause 32(3B) provides that a person will be declared 'not fit and proper' only after being given a reasonable opportunity to respond.
+3. The period for which a person declared 'not fit and proper' is ineligible to apply for any registration has been omitted, suggesting no specific duration is specified in the order.
+4. The waiting period for considering an application for registration as an intermediary when a notice to show cause has been issued has been revised from one year to six months.
+5. The provision regarding the impact of a disqualification of an associate or group entity on the 'fit and proper person' criteria of the applicant or intermediary has been substituted, now stating that the declaration only affects if the same event occurs with the applicant or intermediary or any other person referred in clause (2).
+**Existing Provision:**
+Before these amendments, there were no provisions for immediate reporting of events under sub-clause (b) of clause (3), and the waiting period for considering applications was one year. The impact of a disqualification of an associate or group entity on the 'fit and proper person' criteria was more stringent.
+**Compliance Implications:**
+Listed entities and intermediaries should familiarize themselves with these amendments and ensure timely reporting of events as per the revised guidelines to avoid any potential penalties or delays in registration processes. They should also update their internal policies and procedures accordingly.
+**SEBI Newsletter Summary**
+Date: 16th April, 2026
+Effective Date: 15th April, 2026
+**Amendment Announcement**
+SEBI has amended the 'fit and proper person' criteria for applicants and intermediaries, as well as their key personnel.
+*What changed:* The criteria for determining a person as 'not fit and proper' has been expanded to include:
+  - an order of conviction passed against the person by a court for any economic offence or offence involving moral turpitude;
+  - winding up orders against such person;
+  - persons categorized as wilful defaulters.
+*What existed earlier:* Prior disqualifications included restraint, prohibition, or debarment orders, recovery proceedings initiated by the Board, and various other conditions.
+*Compliance Implication:* Intermediaries must inform SEBI within fifteen working days of any event under sub-clause (b) of clause (3), if a person subject to such criteria is associated with them.
+**Action Point for Listed Entities/Intermediaries:** Ensure compliance with the updated 'fit and proper person' criteria when assessing key personnel. Be aware of changes in status for any individuals associated with your organization that may trigger reporting obligations to SEBI.
+**SEBI Newsletter**
+*SEBI has amended certain provisions related to intermediaries effective 15th April, 2026.*
+**Key Highlights:**
+1. Newly Inserted Provision: The term "days" now means calendar days unless otherwise specified in these regulations. This provides clarity on the interpretation of timeframes within the regulations. [Inserted by the Securities and Exchange Board of India (Intermediaries) (Amendment) Regulations, 2026]
+2. Changes in Application Process: Applications for grant of a certificate to act as an intermediary are now required to be made through the relevant self regulatory organization on the date specified by SEBI, as opposed to directly to SEBI. [Inserted by the Securities and Exchange Board of India (Intermediaries) (Amendment) Regulations, 2026]
+**Existing Provisions:**
+Previously, the term "days" was not explicitly defined within these regulations. Applications for registration were made directly to SEBI, depending on the type of intermediary.
+**Compliance Implication:**
+Intermediaries should familiarize themselves with the new definition of "days" and adjust their internal processes accordingly. They must also comply with the revised application process by submitting applications through the relevant self regulatory organization as specified by SEBI.
+**SEBI Newsletter Summary**
+**Date:** April 15, 2026
+**Effective Date:** April 15, 2026
+**Amendment Overview:**
+- SEBI has introduced and substituted provisions related to the 'fit and proper person' criteria for intermediaries.
+**Changes &amp; Implications:**
+1. A new clause (3A) requires applicants or intermediaries to inform the Board within fifteen working days of any event under sub-clause (b) of clause (3).
+2. The period during which a person declared unfi</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>SECURITIES AND EXCHANGE BOARD OF INDIA
-NOTIFICATION
-Mumbai, the 16th April, 2026
-SECURITIES AND EXCHANGE BOARD OF INDIA (REAL ESTATE INVESTMENT TRUSTS) (AMENDMENT) REGULATIONS, 2026
-No. SEBI/LAD-NRO/GN/2026/302.–– In exercise of the powers conferred under Section 30 read with Sections 11 and 12 of the Securities and Exchange Board of India Act, 1992 (15 of 1992), the Board hereby makes the following regulations to further amend the Securities and Exchange Board of India (Real Estate Investment Trusts) Regulations, 2014, namely: –
-1. These regulations may be called the Securities and Exchange Board of India (Real Estate Investment Trusts) (Amendment) Regulations, 2026.
-2. They shall come into force on the date of their publication in the Official Gazette.
-[भाग III—खण् ड 4]
-भारत का रािपत्र : असाधारण
-3.
-In the Securities and Exchange Board of India (Real Estate Investment Trusts) Regulations, 2014, ─
-I.
-in regulation 2, in sub-regulation (1),
-a.
-in clause (ta),
-i. the number “12” appearing after the words “credit risk value is at least” shall be
-substituted with the number “10”;
-ii. after the words and symbol “Class A-I” and before the words “in the potential risk
-class matrix” the words and symbol “or Class B-I” shall be inserted;
-iii. the words and symbols “government securities, treasury bills, repo on government securities” shall be substituted with the words and symbols “Government Securities, treasury bills, repo on Government Securities”;
-II.
-in regulation 18, in sub-regulation (5), in clause (i),
-a.
-the number “12” appearing after the words “credit risk value is at least” shall be substituted with the number “10”;
-b. after the words and symbol “Class A-I” and before the words “in the potential risk class
-matrix” the words and symbol “or Class B-I” shall be inserted.
-BABITHA RAYUDU, Executive Director
-[ADVT.-III/4/Exty./45/2026-27]
-Note:
-1. The Securities and Exchange Board of India (Real Estate Investment Trusts) Regulations, 2014 was published in the Gazette of India on September 26, 2014 vide notification No. LAD-NRO/GN/2014- 15/11/1576 and was last amended on December 11, 2025 by the Securities and Exchange Board of India (Real Estate Investment Trusts) (Third Amendment) Regulations, 2025 vide notification No. SEBI/LAD-NRO/GN/2025/287.
-Uploaded by Dte. of Printing at Government of India Press, Ring Road, Mayapuri, New Delhi-110064 and Published by the Controller of Publications, Delhi-110054.
-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SEBI</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Regulations</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Securities and Exchange Board of India (Intermediaries) (Amendment) Regulations, 2026</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.sebi.gov.in/sebi_data/attachdocs/apr-2026/1776419077625.pdf</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Securities_and_Exchange_Board_of_India_Intermediaries_Amendment_Regulations_2026_1c146097.pdf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Regulations/2026/April/Securities_and_Exchange_Board_of_India_Intermediaries_Amendment_Regulations_2026_1c146097.pdf</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>15th April, 2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Securities and Exchange Board of India (Intermediaries) (Amendment) Regulations, 2026 dated 2026-04-16
-Effective date - 15th April, 2026</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
         <is>
           <t>SECURITIES AND EXCHANGE BOARD OF INDIA NOTIFICATION Mumbai, the 15th April, 2026
 SECURITIES AND EXCHANGE BOARD OF INDIA (INTERMEDIARIES) (AMENDMENT) REGULATIONS, 2026
